--- a/jogos_2025-07-10.xlsx
+++ b/jogos_2025-07-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -199,16 +199,10 @@
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>CRB</t>
   </si>
   <si>
     <t>Atlético GO</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
   </si>
   <si>
     <t>Coritiba</t>
@@ -581,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -771,7 +765,7 @@
         <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -786,43 +780,43 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -837,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -849,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -861,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -915,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD2" s="3">
         <v>45848.79166666666</v>
@@ -929,7 +923,7 @@
         <v>45848</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
@@ -941,142 +935,142 @@
         <v>61</v>
       </c>
       <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
         <v>64</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
       <c r="L3">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1085,182 +1079,12 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" s="3">
-        <v>45848.79166666666</v>
-      </c>
-    </row>
-    <row r="4" spans="1:56">
-      <c r="A4" s="2">
-        <v>45848</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4">
-        <v>2.46</v>
-      </c>
-      <c r="M4">
-        <v>2.68</v>
-      </c>
-      <c r="N4">
-        <v>2.94</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>1.55</v>
-      </c>
-      <c r="AA4">
-        <v>2.39</v>
-      </c>
-      <c r="AB4">
-        <v>2.7</v>
-      </c>
-      <c r="AC4">
-        <v>1.44</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="3">
         <v>45848.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-10.xlsx
+++ b/jogos_2025-07-10.xlsx
@@ -783,13 +783,13 @@
         <v>64</v>
       </c>
       <c r="L2">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="M2">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>1.91</v>
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB2">
         <v>2.7</v>
@@ -971,28 +971,28 @@
         <v>2.25</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T3">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V3">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="W3">
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y3">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Z3">
         <v>1.53</v>
@@ -1001,28 +1001,28 @@
         <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AD3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
         <v>65</v>
@@ -1043,34 +1043,34 @@
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AS3">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="AT3">
-        <v>4.46</v>
+        <v>2.9</v>
       </c>
       <c r="AU3">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="AV3">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AW3">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AX3">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AY3">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3">
         <v>0</v>

--- a/jogos_2025-07-10.xlsx
+++ b/jogos_2025-07-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>Date</t>
   </si>
@@ -125,60 +125,6 @@
   </si>
   <si>
     <t>awayGoals</t>
-  </si>
-  <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
   </si>
   <si>
     <t>DateTime</t>
@@ -575,10 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,79 +639,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45848</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -780,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="L2">
         <v>2.45</v>
@@ -855,87 +747,33 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="AK2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.91</v>
-      </c>
-      <c r="BC2">
-        <v>2.4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>47</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45848.79166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45848</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -950,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="L3">
         <v>2.46</v>
@@ -1025,66 +863,12 @@
         <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="AK3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AL3">
-        <v>1.4</v>
-      </c>
-      <c r="AM3">
-        <v>1.35</v>
-      </c>
-      <c r="AN3">
-        <v>1.53</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.29</v>
-      </c>
-      <c r="AQ3">
-        <v>1.5</v>
-      </c>
-      <c r="AR3">
-        <v>1.8</v>
-      </c>
-      <c r="AS3">
-        <v>2.25</v>
-      </c>
-      <c r="AT3">
-        <v>2.9</v>
-      </c>
-      <c r="AU3">
-        <v>3.3</v>
-      </c>
-      <c r="AV3">
-        <v>2.4</v>
-      </c>
-      <c r="AW3">
-        <v>1.91</v>
-      </c>
-      <c r="AX3">
-        <v>1.57</v>
-      </c>
-      <c r="AY3">
-        <v>1.36</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.05</v>
-      </c>
-      <c r="BC3">
-        <v>2.25</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>47</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45848.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-10.xlsx
+++ b/jogos_2025-07-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -130,9 +130,6 @@
     <t>DateTime</t>
   </si>
   <si>
-    <t>19:00</t>
-  </si>
-  <si>
     <t>21:35</t>
   </si>
   <si>
@@ -142,13 +139,7 @@
     <t>2025</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>CRB</t>
-  </si>
-  <si>
-    <t>Atlético GO</t>
   </si>
   <si>
     <t>Coritiba</t>
@@ -521,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -648,16 +639,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>42</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -672,203 +663,87 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L2">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="M2">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q2">
+        <v>2.25</v>
+      </c>
+      <c r="R2">
+        <v>1.59</v>
+      </c>
+      <c r="S2">
+        <v>2.27</v>
+      </c>
+      <c r="T2">
+        <v>3.4</v>
+      </c>
+      <c r="U2">
+        <v>1.29</v>
+      </c>
+      <c r="V2">
+        <v>9</v>
+      </c>
+      <c r="W2">
+        <v>1.03</v>
+      </c>
+      <c r="X2">
+        <v>1.08</v>
+      </c>
+      <c r="Y2">
+        <v>6.38</v>
+      </c>
+      <c r="Z2">
+        <v>1.54</v>
+      </c>
+      <c r="AA2">
         <v>2.4</v>
       </c>
-      <c r="R2">
-        <v>1.57</v>
-      </c>
-      <c r="S2">
-        <v>2.25</v>
-      </c>
-      <c r="T2">
-        <v>3.75</v>
-      </c>
-      <c r="U2">
-        <v>1.25</v>
-      </c>
-      <c r="V2">
-        <v>13</v>
-      </c>
-      <c r="W2">
-        <v>1.04</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>1.5</v>
-      </c>
-      <c r="AA2">
-        <v>2.37</v>
-      </c>
       <c r="AB2">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AC2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL2" s="3">
-        <v>45848.79166666666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38">
-      <c r="A3" s="2">
-        <v>45848</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3">
-        <v>2.46</v>
-      </c>
-      <c r="M3">
-        <v>2.68</v>
-      </c>
-      <c r="N3">
-        <v>2.94</v>
-      </c>
-      <c r="O3">
-        <v>2.05</v>
-      </c>
-      <c r="P3">
-        <v>6</v>
-      </c>
-      <c r="Q3">
-        <v>2.25</v>
-      </c>
-      <c r="R3">
-        <v>1.55</v>
-      </c>
-      <c r="S3">
-        <v>2.2</v>
-      </c>
-      <c r="T3">
-        <v>3.6</v>
-      </c>
-      <c r="U3">
-        <v>1.25</v>
-      </c>
-      <c r="V3">
-        <v>8.5</v>
-      </c>
-      <c r="W3">
-        <v>1.02</v>
-      </c>
-      <c r="X3">
-        <v>1.12</v>
-      </c>
-      <c r="Y3">
-        <v>5.75</v>
-      </c>
-      <c r="Z3">
-        <v>1.53</v>
-      </c>
-      <c r="AA3">
-        <v>2.25</v>
-      </c>
-      <c r="AB3">
-        <v>2.55</v>
-      </c>
-      <c r="AC3">
-        <v>1.45</v>
-      </c>
-      <c r="AD3">
-        <v>5.3</v>
-      </c>
-      <c r="AE3">
-        <v>1.15</v>
-      </c>
-      <c r="AF3">
-        <v>2.2</v>
-      </c>
-      <c r="AG3">
-        <v>1.65</v>
-      </c>
-      <c r="AH3">
-        <v>10</v>
-      </c>
-      <c r="AI3">
-        <v>1.04</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL3" s="3">
         <v>45848.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-10.xlsx
+++ b/jogos_2025-07-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -145,10 +145,13 @@
     <t>Coritiba</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -666,13 +669,13 @@
         <v>43</v>
       </c>
       <c r="L2">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M2">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>2.05</v>
@@ -684,64 +687,64 @@
         <v>2.25</v>
       </c>
       <c r="R2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="T2">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y2">
-        <v>6.38</v>
+        <v>5.75</v>
       </c>
       <c r="Z2">
         <v>1.54</v>
       </c>
       <c r="AA2">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AB2">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AC2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AD2">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG2">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
         <v>44</v>
       </c>
       <c r="AK2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AL2" s="3">
         <v>45848.89930555555</v>
